--- a/REDCap/Input Sheets/Excel Sheets/B_LR_Low Res-TEST.xlsx
+++ b/REDCap/Input Sheets/Excel Sheets/B_LR_Low Res-TEST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvuko\CBOTH_Summer_2026\REDCap\Input Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvuko\CBOTH_Summer_2026\REDCap\Input Sheets\Excel Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56168B2B-F26B-41FE-90DD-4803CF8CF0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1DAA43-FEDE-4451-918F-B81A6FB29D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{312B8B40-1855-4431-9E18-FFD4D8B3CAF7}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="110">
   <si>
     <t>Please insert data from only 1 unit per Round</t>
   </si>
@@ -397,6 +397,12 @@
   </si>
   <si>
     <t>2.08 kg</t>
+  </si>
+  <si>
+    <t>Transfusion ID</t>
+  </si>
+  <si>
+    <t>Tele ID</t>
   </si>
 </sst>
 </file>
@@ -558,7 +564,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -668,12 +674,68 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -784,6 +846,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -803,29 +891,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1174,23 +1252,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="25.8">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -1232,19 +1310,19 @@
       <c r="AZ1" s="4"/>
     </row>
     <row r="2" spans="1:52" ht="25.8">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -1351,8 +1429,8 @@
       <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="4"/>
@@ -1465,7 +1543,7 @@
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="51">
         <v>46053</v>
       </c>
       <c r="C6" s="49"/>
@@ -1523,10 +1601,12 @@
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48">
+      <c r="B7" s="42">
         <v>32</v>
       </c>
-      <c r="C7" s="49"/>
+      <c r="C7" s="45">
+        <v>0.45</v>
+      </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="1"/>
@@ -1577,14 +1657,14 @@
       <c r="AY7" s="4"/>
       <c r="AZ7" s="4"/>
     </row>
-    <row r="8" spans="1:52" ht="26.4" thickBot="1">
+    <row r="8" spans="1:52" ht="25.8">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="48">
+      <c r="B8" s="60">
         <v>43</v>
       </c>
-      <c r="C8" s="49"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="1"/>
@@ -1635,10 +1715,14 @@
       <c r="AY8" s="4"/>
       <c r="AZ8" s="4"/>
     </row>
-    <row r="9" spans="1:52">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+    <row r="9" spans="1:52" ht="16.2" thickBot="1">
+      <c r="A9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="63">
+        <v>8975697</v>
+      </c>
+      <c r="C9" s="62"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -1689,995 +1773,647 @@
       <c r="AY9" s="4"/>
       <c r="AZ9" s="4"/>
     </row>
-    <row r="10" spans="1:52">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="S10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="T10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="U10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="V10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="X10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AQ10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AS10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AT10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AU10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AX10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AY10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AZ10" s="11" t="s">
+    <row r="13" spans="1:52">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AR13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AT13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AX13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AZ13" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:52" ht="14.4" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="10" t="s">
+    <row r="14" spans="1:52" ht="14.4" customHeight="1">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E14" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G14" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="12" t="s">
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="53" t="s">
+      <c r="N14" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
-      <c r="R11" s="55" t="s">
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="55"/>
-      <c r="AA11" s="52" t="s">
+      <c r="S14" s="50"/>
+      <c r="T14" s="50"/>
+      <c r="U14" s="50"/>
+      <c r="V14" s="50"/>
+      <c r="W14" s="50"/>
+      <c r="X14" s="50"/>
+      <c r="Y14" s="50"/>
+      <c r="Z14" s="50"/>
+      <c r="AA14" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52" t="s">
+      <c r="AB14" s="46"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="46"/>
+      <c r="AE14" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="53" t="s">
+      <c r="AF14" s="46"/>
+      <c r="AG14" s="46"/>
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="AJ11" s="53"/>
-      <c r="AK11" s="53"/>
-      <c r="AL11" s="53"/>
-      <c r="AM11" s="53"/>
-      <c r="AN11" s="53"/>
-      <c r="AO11" s="53"/>
-      <c r="AP11" s="53"/>
-      <c r="AQ11" s="53"/>
-      <c r="AR11" s="53"/>
-      <c r="AS11" s="53"/>
-      <c r="AT11" s="53"/>
-      <c r="AU11" s="53"/>
-      <c r="AV11" s="53"/>
-      <c r="AW11" s="53"/>
-      <c r="AX11" s="53"/>
-      <c r="AY11" s="53" t="s">
+      <c r="AJ14" s="47"/>
+      <c r="AK14" s="47"/>
+      <c r="AL14" s="47"/>
+      <c r="AM14" s="47"/>
+      <c r="AN14" s="47"/>
+      <c r="AO14" s="47"/>
+      <c r="AP14" s="47"/>
+      <c r="AQ14" s="47"/>
+      <c r="AR14" s="47"/>
+      <c r="AS14" s="47"/>
+      <c r="AT14" s="47"/>
+      <c r="AU14" s="47"/>
+      <c r="AV14" s="47"/>
+      <c r="AW14" s="47"/>
+      <c r="AX14" s="47"/>
+      <c r="AY14" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="AZ11" s="53"/>
-    </row>
-    <row r="12" spans="1:52" ht="15.6">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="R12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="S12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="T12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="U12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="V12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="W12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="X12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA12" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB12" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC12" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD12" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE12" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF12" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG12" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH12" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AK12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AL12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AO12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AR12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AT12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AU12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AV12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AW12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AX12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AY12" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AZ12" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:52" ht="15" thickBot="1">
-      <c r="A13" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="N13" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="S13" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="T13" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="U13" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="V13" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="W13" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="X13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y13" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z13" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA13" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB13" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC13" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD13" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE13" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF13" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG13" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI13" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ13" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK13" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL13" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="AM13" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN13" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AO13" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP13" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ13" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="AR13" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="AS13" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AT13" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU13" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV13" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW13" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AX13" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY13" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="AZ13" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:52">
-      <c r="A14" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="28">
-        <v>0.13155092592592593</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="29">
-        <v>61</v>
-      </c>
-      <c r="E14" s="29">
-        <v>232</v>
-      </c>
-      <c r="F14" s="29">
-        <v>39</v>
-      </c>
-      <c r="G14" s="30">
-        <v>3.79</v>
-      </c>
-      <c r="H14" s="36">
-        <v>3.61</v>
-      </c>
-      <c r="I14" s="30">
-        <v>32.99</v>
-      </c>
-      <c r="J14" s="30">
-        <v>239</v>
-      </c>
-      <c r="K14" s="30">
-        <v>4.82</v>
-      </c>
-      <c r="L14" s="30">
-        <v>44.85</v>
-      </c>
-      <c r="M14" s="38">
-        <v>0.19261740642916964</v>
-      </c>
-      <c r="N14" s="36">
-        <v>7.9</v>
-      </c>
-      <c r="O14" s="40">
-        <v>10.25</v>
-      </c>
-      <c r="P14" s="40">
-        <v>35.94</v>
-      </c>
-      <c r="Q14" s="40">
-        <v>81.8</v>
-      </c>
-      <c r="R14" s="39">
-        <v>68.27</v>
-      </c>
-      <c r="S14" s="39">
-        <v>193</v>
-      </c>
-      <c r="T14" s="39">
-        <v>224</v>
-      </c>
-      <c r="U14" s="39">
-        <v>1.86</v>
-      </c>
-      <c r="V14" s="39">
-        <v>12.58</v>
-      </c>
-      <c r="W14" s="39">
-        <v>300</v>
-      </c>
-      <c r="X14" s="39">
-        <v>59.69</v>
-      </c>
-      <c r="Y14" s="39">
-        <v>146.37</v>
-      </c>
-      <c r="Z14" s="39">
-        <v>3</v>
-      </c>
-      <c r="AA14" s="30">
-        <v>2.11</v>
-      </c>
-      <c r="AB14" s="30">
-        <v>1.58</v>
-      </c>
-      <c r="AC14" s="30">
-        <v>67.489999999999995</v>
-      </c>
-      <c r="AD14" s="30">
-        <v>55.66</v>
-      </c>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="30">
-        <v>31.84</v>
-      </c>
-      <c r="AG14" s="33"/>
-      <c r="AH14" s="33"/>
-      <c r="AI14" s="9"/>
-      <c r="AJ14" s="9"/>
-      <c r="AK14" s="9"/>
-      <c r="AL14" s="9"/>
-      <c r="AM14" s="9"/>
-      <c r="AN14" s="9"/>
-      <c r="AO14" s="9"/>
-      <c r="AP14" s="9"/>
-      <c r="AQ14" s="9"/>
-      <c r="AR14" s="9"/>
-      <c r="AS14" s="9"/>
-      <c r="AT14" s="9"/>
-      <c r="AU14" s="9"/>
-      <c r="AV14" s="9"/>
-      <c r="AW14" s="9"/>
-      <c r="AX14" s="9"/>
-      <c r="AY14" s="9"/>
-      <c r="AZ14" s="9"/>
+      <c r="AZ14" s="47"/>
     </row>
     <row r="15" spans="1:52" ht="15.6">
-      <c r="A15" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="28">
-        <v>0.91518518518518521</v>
-      </c>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="29">
+        <v>22</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="S15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="U15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="V15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="W15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="X15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC15" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AU15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AV15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AW15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AX15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY15" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AZ15" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:52" ht="15" thickBot="1">
+      <c r="A16" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="S16" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="T16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="U16" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="V16" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="W16" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="X16" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y16" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z16" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA16" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="12">
-        <v>210</v>
-      </c>
-      <c r="F15" s="12">
-        <v>39</v>
-      </c>
-      <c r="G15" s="32">
-        <v>9.9700000000000006</v>
-      </c>
-      <c r="H15" s="34">
-        <v>3.43</v>
-      </c>
-      <c r="I15" s="34">
-        <v>35.81</v>
-      </c>
-      <c r="J15" s="30">
-        <v>321</v>
-      </c>
-      <c r="K15" s="30">
-        <v>5.08</v>
-      </c>
-      <c r="L15" s="37">
-        <v>73.87</v>
-      </c>
-      <c r="M15" s="38">
-        <v>0.33389834339051233</v>
-      </c>
-      <c r="N15" s="39">
-        <v>6.87</v>
-      </c>
-      <c r="O15" s="40">
-        <v>5.47</v>
-      </c>
-      <c r="P15" s="40">
-        <v>31.16</v>
-      </c>
-      <c r="Q15" s="40">
-        <v>80.56</v>
-      </c>
-      <c r="R15" s="30">
-        <v>93.45</v>
-      </c>
-      <c r="S15" s="30">
-        <v>191</v>
-      </c>
-      <c r="T15" s="30">
-        <v>113</v>
-      </c>
-      <c r="U15" s="30">
-        <v>1.4</v>
-      </c>
-      <c r="V15" s="30">
-        <v>23.32</v>
-      </c>
-      <c r="W15" s="30">
-        <v>263</v>
-      </c>
-      <c r="X15" s="30">
-        <v>99.3</v>
-      </c>
-      <c r="Y15" s="30">
-        <v>350.98</v>
-      </c>
-      <c r="Z15" s="30">
-        <v>2</v>
-      </c>
-      <c r="AA15" s="30">
-        <v>5.82</v>
-      </c>
-      <c r="AB15" s="30">
-        <v>1.74</v>
-      </c>
-      <c r="AC15" s="30">
-        <v>66.84</v>
-      </c>
-      <c r="AD15" s="30">
-        <v>64.540000000000006</v>
-      </c>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="41">
-        <v>10.57</v>
-      </c>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="9"/>
-      <c r="AJ15" s="9"/>
-      <c r="AK15" s="9"/>
-      <c r="AL15" s="9"/>
-      <c r="AM15" s="9"/>
-      <c r="AN15" s="9"/>
-      <c r="AO15" s="9"/>
-      <c r="AP15" s="9"/>
-      <c r="AQ15" s="9"/>
-      <c r="AR15" s="9"/>
-      <c r="AS15" s="9"/>
-      <c r="AT15" s="9"/>
-      <c r="AU15" s="9"/>
-      <c r="AV15" s="9"/>
-      <c r="AW15" s="9"/>
-      <c r="AX15" s="9"/>
-      <c r="AY15" s="9"/>
-      <c r="AZ15" s="9"/>
+      <c r="AB16" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC16" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD16" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE16" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF16" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG16" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH16" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI16" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ16" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK16" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL16" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN16" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO16" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP16" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ16" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR16" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS16" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT16" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU16" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV16" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW16" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX16" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ16" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="16" spans="1:52" ht="15.6">
-      <c r="A16" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="28">
-        <v>0.9629861111111111</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="29">
-        <v>50</v>
-      </c>
-      <c r="E16" s="12">
-        <v>239</v>
-      </c>
-      <c r="F16" s="12">
-        <v>44</v>
-      </c>
-      <c r="G16" s="32">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="H16" s="34">
-        <v>4.03</v>
-      </c>
-      <c r="I16" s="34">
-        <v>37.83</v>
-      </c>
-      <c r="J16" s="30">
-        <v>159</v>
-      </c>
-      <c r="K16" s="30">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="L16" s="37">
-        <v>73.209999999999994</v>
-      </c>
-      <c r="M16" s="38">
-        <v>0.28164733491065069</v>
-      </c>
-      <c r="N16" s="39">
-        <v>5.39</v>
-      </c>
-      <c r="O16" s="40">
-        <v>5.4</v>
-      </c>
-      <c r="P16" s="40">
-        <v>35.75</v>
-      </c>
-      <c r="Q16" s="40">
-        <v>89.8</v>
-      </c>
-      <c r="R16" s="30">
-        <v>136.16</v>
-      </c>
-      <c r="S16" s="30">
-        <v>138</v>
-      </c>
-      <c r="T16" s="30">
-        <v>161</v>
-      </c>
-      <c r="U16" s="30">
-        <v>1.29</v>
-      </c>
-      <c r="V16" s="30">
-        <v>14.23</v>
-      </c>
-      <c r="W16" s="30">
-        <v>261</v>
-      </c>
-      <c r="X16" s="30">
-        <v>71.36</v>
-      </c>
-      <c r="Y16" s="30">
-        <v>366.24</v>
-      </c>
-      <c r="Z16" s="30">
-        <v>4</v>
-      </c>
-      <c r="AA16" s="30">
-        <v>5.69</v>
-      </c>
-      <c r="AB16" s="30">
-        <v>1.83</v>
-      </c>
-      <c r="AC16" s="30">
-        <v>65.19</v>
-      </c>
-      <c r="AD16" s="30">
-        <v>52.34</v>
-      </c>
-      <c r="AE16" s="30"/>
-      <c r="AF16" s="41">
-        <v>18.010000000000002</v>
-      </c>
-      <c r="AG16" s="35"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="9"/>
-      <c r="AJ16" s="9"/>
-      <c r="AK16" s="9"/>
-      <c r="AL16" s="9"/>
-      <c r="AM16" s="9"/>
-      <c r="AN16" s="9"/>
-      <c r="AO16" s="9"/>
-      <c r="AP16" s="9"/>
-      <c r="AQ16" s="9"/>
-      <c r="AR16" s="9"/>
-      <c r="AS16" s="9"/>
-      <c r="AT16" s="9"/>
-      <c r="AU16" s="9"/>
-      <c r="AV16" s="9"/>
-      <c r="AW16" s="9"/>
-      <c r="AX16" s="9"/>
-      <c r="AY16" s="9"/>
-      <c r="AZ16" s="9"/>
-    </row>
-    <row r="17" spans="1:52" ht="15.6">
-      <c r="A17" s="22">
-        <v>0.1</v>
+    <row r="17" spans="1:52">
+      <c r="A17" s="20" t="s">
+        <v>90</v>
       </c>
       <c r="B17" s="28">
-        <v>0.48321759259259262</v>
+        <v>0.13155092592592593</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D17" s="29">
-        <v>51</v>
-      </c>
-      <c r="E17" s="12">
-        <v>227</v>
-      </c>
-      <c r="F17" s="12">
-        <v>36</v>
-      </c>
-      <c r="G17" s="32">
-        <v>7.78</v>
-      </c>
-      <c r="H17" s="34">
-        <v>9.9600000000000009</v>
-      </c>
-      <c r="I17" s="34">
-        <v>22.57</v>
+        <v>61</v>
+      </c>
+      <c r="E17" s="29">
+        <v>232</v>
+      </c>
+      <c r="F17" s="29">
+        <v>39</v>
+      </c>
+      <c r="G17" s="30">
+        <v>3.79</v>
+      </c>
+      <c r="H17" s="36">
+        <v>3.61</v>
+      </c>
+      <c r="I17" s="30">
+        <v>32.99</v>
       </c>
       <c r="J17" s="30">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="K17" s="30">
+        <v>4.82</v>
+      </c>
+      <c r="L17" s="30">
+        <v>44.85</v>
+      </c>
+      <c r="M17" s="38">
+        <v>0.19261740642916964</v>
+      </c>
+      <c r="N17" s="36">
+        <v>7.9</v>
+      </c>
+      <c r="O17" s="40">
+        <v>10.25</v>
+      </c>
+      <c r="P17" s="40">
+        <v>35.94</v>
+      </c>
+      <c r="Q17" s="40">
+        <v>81.8</v>
+      </c>
+      <c r="R17" s="39">
+        <v>68.27</v>
+      </c>
+      <c r="S17" s="39">
+        <v>193</v>
+      </c>
+      <c r="T17" s="39">
+        <v>224</v>
+      </c>
+      <c r="U17" s="39">
+        <v>1.86</v>
+      </c>
+      <c r="V17" s="39">
+        <v>12.58</v>
+      </c>
+      <c r="W17" s="39">
+        <v>300</v>
+      </c>
+      <c r="X17" s="39">
+        <v>59.69</v>
+      </c>
+      <c r="Y17" s="39">
+        <v>146.37</v>
+      </c>
+      <c r="Z17" s="39">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="30">
+        <v>2.11</v>
+      </c>
+      <c r="AB17" s="30">
         <v>1.58</v>
       </c>
-      <c r="L17" s="37">
-        <v>46.89</v>
-      </c>
-      <c r="M17" s="38">
-        <v>7.2989632950406266E-2</v>
-      </c>
-      <c r="N17" s="39">
-        <v>7.87</v>
-      </c>
-      <c r="O17" s="40">
-        <v>11.92</v>
-      </c>
-      <c r="P17" s="40">
-        <v>31.01</v>
-      </c>
-      <c r="Q17" s="40">
-        <v>87.54</v>
-      </c>
-      <c r="R17" s="30">
-        <v>143.65</v>
-      </c>
-      <c r="S17" s="30">
-        <v>161</v>
-      </c>
-      <c r="T17" s="30">
-        <v>84</v>
-      </c>
-      <c r="U17" s="30">
-        <v>1.43</v>
-      </c>
-      <c r="V17" s="30">
-        <v>25.29</v>
-      </c>
-      <c r="W17" s="30">
-        <v>152</v>
-      </c>
-      <c r="X17" s="30">
-        <v>54.9</v>
-      </c>
-      <c r="Y17" s="30">
-        <v>539.91</v>
-      </c>
-      <c r="Z17" s="30">
-        <v>2</v>
-      </c>
-      <c r="AA17" s="30">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="AB17" s="30">
-        <v>1.61</v>
-      </c>
       <c r="AC17" s="30">
-        <v>58.8</v>
+        <v>67.489999999999995</v>
       </c>
       <c r="AD17" s="30">
-        <v>64.02</v>
+        <v>55.66</v>
       </c>
       <c r="AE17" s="30"/>
-      <c r="AF17" s="41">
-        <v>27.37</v>
-      </c>
-      <c r="AG17" s="35"/>
-      <c r="AH17" s="35"/>
+      <c r="AF17" s="30">
+        <v>31.84</v>
+      </c>
+      <c r="AG17" s="33"/>
+      <c r="AH17" s="33"/>
       <c r="AI17" s="9"/>
       <c r="AJ17" s="9"/>
       <c r="AK17" s="9"/>
@@ -2698,99 +2434,99 @@
       <c r="AZ17" s="9"/>
     </row>
     <row r="18" spans="1:52" ht="15.6">
-      <c r="A18" s="23">
-        <v>7.4999999999999997E-2</v>
+      <c r="A18" s="12" t="s">
+        <v>92</v>
       </c>
       <c r="B18" s="28">
-        <v>0.41658564814814814</v>
+        <v>0.91518518518518521</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D18" s="29">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="E18" s="12">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="F18" s="12">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" s="32">
-        <v>7.36</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="H18" s="34">
-        <v>6.24</v>
+        <v>3.43</v>
       </c>
       <c r="I18" s="34">
-        <v>29.02</v>
+        <v>35.81</v>
       </c>
       <c r="J18" s="30">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="K18" s="30">
-        <v>5.57</v>
+        <v>5.08</v>
       </c>
       <c r="L18" s="37">
-        <v>47.57</v>
+        <v>73.87</v>
       </c>
       <c r="M18" s="38">
-        <v>0.11819220830848737</v>
+        <v>0.33389834339051233</v>
       </c>
       <c r="N18" s="39">
-        <v>3.93</v>
+        <v>6.87</v>
       </c>
       <c r="O18" s="40">
-        <v>7.18</v>
+        <v>5.47</v>
       </c>
       <c r="P18" s="40">
-        <v>35.6</v>
+        <v>31.16</v>
       </c>
       <c r="Q18" s="40">
-        <v>85.68</v>
+        <v>80.56</v>
       </c>
       <c r="R18" s="30">
-        <v>59.43</v>
+        <v>93.45</v>
       </c>
       <c r="S18" s="30">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="T18" s="30">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="U18" s="30">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V18" s="30">
-        <v>24.69</v>
+        <v>23.32</v>
       </c>
       <c r="W18" s="30">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="X18" s="30">
-        <v>99.91</v>
+        <v>99.3</v>
       </c>
       <c r="Y18" s="30">
-        <v>543.76</v>
+        <v>350.98</v>
       </c>
       <c r="Z18" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA18" s="30">
-        <v>4.7300000000000004</v>
+        <v>5.82</v>
       </c>
       <c r="AB18" s="30">
-        <v>2.27</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" s="30">
-        <v>77.95</v>
+        <v>66.84</v>
       </c>
       <c r="AD18" s="30">
-        <v>64.78</v>
+        <v>64.540000000000006</v>
       </c>
       <c r="AE18" s="30"/>
       <c r="AF18" s="41">
-        <v>65.98</v>
+        <v>10.57</v>
       </c>
       <c r="AG18" s="35"/>
       <c r="AH18" s="35"/>
@@ -2814,99 +2550,99 @@
       <c r="AZ18" s="9"/>
     </row>
     <row r="19" spans="1:52" ht="15.6">
-      <c r="A19" s="22">
-        <v>0.05</v>
+      <c r="A19" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="B19" s="28">
-        <v>0.20196759259259259</v>
+        <v>0.9629861111111111</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D19" s="29">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E19" s="12">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F19" s="12">
         <v>44</v>
       </c>
       <c r="G19" s="32">
-        <v>2.61</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="H19" s="34">
-        <v>7.5</v>
+        <v>4.03</v>
       </c>
       <c r="I19" s="34">
-        <v>33.86</v>
+        <v>37.83</v>
       </c>
       <c r="J19" s="30">
-        <v>250</v>
+        <v>159</v>
       </c>
       <c r="K19" s="30">
-        <v>4.7699999999999996</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="L19" s="37">
-        <v>43.72</v>
+        <v>73.209999999999994</v>
       </c>
       <c r="M19" s="38">
-        <v>9.0377260981912136E-2</v>
+        <v>0.28164733491065069</v>
       </c>
       <c r="N19" s="39">
-        <v>1.1299999999999999</v>
+        <v>5.39</v>
       </c>
       <c r="O19" s="40">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="P19" s="40">
-        <v>34.32</v>
+        <v>35.75</v>
       </c>
       <c r="Q19" s="40">
-        <v>83.94</v>
+        <v>89.8</v>
       </c>
       <c r="R19" s="30">
-        <v>75.73</v>
+        <v>136.16</v>
       </c>
       <c r="S19" s="30">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="T19" s="30">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="U19" s="30">
-        <v>1.1399999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="V19" s="30">
-        <v>11.24</v>
+        <v>14.23</v>
       </c>
       <c r="W19" s="30">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="X19" s="30">
-        <v>107.7</v>
+        <v>71.36</v>
       </c>
       <c r="Y19" s="30">
-        <v>583.91</v>
+        <v>366.24</v>
       </c>
       <c r="Z19" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA19" s="30">
-        <v>6.47</v>
+        <v>5.69</v>
       </c>
       <c r="AB19" s="30">
-        <v>2.57</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" s="30">
-        <v>55.29</v>
+        <v>65.19</v>
       </c>
       <c r="AD19" s="30">
-        <v>63.73</v>
+        <v>52.34</v>
       </c>
       <c r="AE19" s="30"/>
       <c r="AF19" s="41">
-        <v>56.17</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="AG19" s="35"/>
       <c r="AH19" s="35"/>
@@ -2929,103 +2665,103 @@
       <c r="AY19" s="9"/>
       <c r="AZ19" s="9"/>
     </row>
-    <row r="20" spans="1:52">
-      <c r="A20" s="23">
-        <v>2.5000000000000001E-2</v>
+    <row r="20" spans="1:52" ht="15.6">
+      <c r="A20" s="22">
+        <v>0.1</v>
       </c>
       <c r="B20" s="28">
-        <v>0.80834490740740739</v>
+        <v>0.48321759259259262</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D20" s="29">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E20" s="12">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F20" s="12">
-        <v>42</v>
-      </c>
-      <c r="G20" s="13">
-        <v>8.6</v>
-      </c>
-      <c r="H20" s="13">
-        <v>7.17</v>
-      </c>
-      <c r="I20" s="13">
-        <v>20.54</v>
+        <v>36</v>
+      </c>
+      <c r="G20" s="32">
+        <v>7.78</v>
+      </c>
+      <c r="H20" s="34">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="I20" s="34">
+        <v>22.57</v>
       </c>
       <c r="J20" s="30">
-        <v>198</v>
+        <v>292</v>
       </c>
       <c r="K20" s="30">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="L20" s="37">
-        <v>35.450000000000003</v>
+        <v>46.89</v>
       </c>
       <c r="M20" s="38">
-        <v>7.6654449525910079E-2</v>
+        <v>7.2989632950406266E-2</v>
       </c>
       <c r="N20" s="39">
-        <v>1.88</v>
+        <v>7.87</v>
       </c>
       <c r="O20" s="40">
-        <v>3.91</v>
+        <v>11.92</v>
       </c>
       <c r="P20" s="40">
-        <v>36.229999999999997</v>
+        <v>31.01</v>
       </c>
       <c r="Q20" s="40">
-        <v>80.63</v>
+        <v>87.54</v>
       </c>
       <c r="R20" s="30">
-        <v>58.86</v>
+        <v>143.65</v>
       </c>
       <c r="S20" s="30">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="T20" s="30">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="U20" s="30">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="V20" s="30">
-        <v>22.6</v>
+        <v>25.29</v>
       </c>
       <c r="W20" s="30">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="X20" s="30">
-        <v>58.44</v>
+        <v>54.9</v>
       </c>
       <c r="Y20" s="30">
-        <v>489.92</v>
+        <v>539.91</v>
       </c>
       <c r="Z20" s="30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA20" s="30">
-        <v>3.32</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="AB20" s="30">
         <v>1.61</v>
       </c>
       <c r="AC20" s="30">
-        <v>74.849999999999994</v>
+        <v>58.8</v>
       </c>
       <c r="AD20" s="30">
-        <v>54.74</v>
+        <v>64.02</v>
       </c>
       <c r="AE20" s="30"/>
       <c r="AF20" s="41">
-        <v>31.16</v>
-      </c>
-      <c r="AG20" s="9"/>
-      <c r="AH20" s="9"/>
+        <v>27.37</v>
+      </c>
+      <c r="AG20" s="35"/>
+      <c r="AH20" s="35"/>
       <c r="AI20" s="9"/>
       <c r="AJ20" s="9"/>
       <c r="AK20" s="9"/>
@@ -3045,100 +2781,100 @@
       <c r="AY20" s="9"/>
       <c r="AZ20" s="9"/>
     </row>
-    <row r="21" spans="1:52">
-      <c r="A21" s="12" t="s">
-        <v>94</v>
+    <row r="21" spans="1:52" ht="15.6">
+      <c r="A21" s="23">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="B21" s="28">
-        <v>0.45627314814814812</v>
+        <v>0.41658564814814814</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D21" s="29">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="E21" s="12">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F21" s="12">
-        <v>36</v>
-      </c>
-      <c r="G21" s="13">
-        <v>4.7</v>
-      </c>
-      <c r="H21" s="13">
-        <v>4.24</v>
-      </c>
-      <c r="I21" s="13">
-        <v>36.08</v>
-      </c>
-      <c r="J21" s="13">
-        <v>140</v>
-      </c>
-      <c r="K21" s="13">
-        <v>2.54</v>
-      </c>
-      <c r="L21" s="13">
-        <v>88.54</v>
+        <v>40</v>
+      </c>
+      <c r="G21" s="32">
+        <v>7.36</v>
+      </c>
+      <c r="H21" s="34">
+        <v>6.24</v>
+      </c>
+      <c r="I21" s="34">
+        <v>29.02</v>
+      </c>
+      <c r="J21" s="30">
+        <v>262</v>
+      </c>
+      <c r="K21" s="30">
+        <v>5.57</v>
+      </c>
+      <c r="L21" s="37">
+        <v>47.57</v>
       </c>
       <c r="M21" s="38">
-        <v>0.32375310808834284</v>
-      </c>
-      <c r="N21" s="31">
-        <v>0.43</v>
-      </c>
-      <c r="O21" s="21">
-        <v>6.43</v>
-      </c>
-      <c r="P21" s="21">
-        <v>37.24</v>
-      </c>
-      <c r="Q21" s="21">
-        <v>85.76</v>
-      </c>
-      <c r="R21" s="31">
-        <v>139.36000000000001</v>
-      </c>
-      <c r="S21" s="31">
-        <v>181</v>
-      </c>
-      <c r="T21" s="31">
-        <v>192</v>
-      </c>
-      <c r="U21" s="31">
-        <v>1.34</v>
-      </c>
-      <c r="V21" s="31">
-        <v>16.010000000000002</v>
-      </c>
-      <c r="W21" s="31">
-        <v>206</v>
-      </c>
-      <c r="X21" s="31">
-        <v>71.52</v>
-      </c>
-      <c r="Y21" s="31">
-        <v>211.14</v>
-      </c>
-      <c r="Z21" s="31">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="9">
-        <v>2.46</v>
-      </c>
-      <c r="AB21" s="9">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="AC21" s="9">
-        <v>55.22</v>
-      </c>
-      <c r="AD21" s="9">
-        <v>57.54</v>
-      </c>
-      <c r="AE21" s="9"/>
-      <c r="AF21" s="35">
-        <v>24.22</v>
+        <v>0.11819220830848737</v>
+      </c>
+      <c r="N21" s="39">
+        <v>3.93</v>
+      </c>
+      <c r="O21" s="40">
+        <v>7.18</v>
+      </c>
+      <c r="P21" s="40">
+        <v>35.6</v>
+      </c>
+      <c r="Q21" s="40">
+        <v>85.68</v>
+      </c>
+      <c r="R21" s="30">
+        <v>59.43</v>
+      </c>
+      <c r="S21" s="30">
+        <v>229</v>
+      </c>
+      <c r="T21" s="30">
+        <v>254</v>
+      </c>
+      <c r="U21" s="30">
+        <v>1.29</v>
+      </c>
+      <c r="V21" s="30">
+        <v>24.69</v>
+      </c>
+      <c r="W21" s="30">
+        <v>306</v>
+      </c>
+      <c r="X21" s="30">
+        <v>99.91</v>
+      </c>
+      <c r="Y21" s="30">
+        <v>543.76</v>
+      </c>
+      <c r="Z21" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="30">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="AB21" s="30">
+        <v>2.27</v>
+      </c>
+      <c r="AC21" s="30">
+        <v>77.95</v>
+      </c>
+      <c r="AD21" s="30">
+        <v>64.78</v>
+      </c>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="41">
+        <v>65.98</v>
       </c>
       <c r="AG21" s="35"/>
       <c r="AH21" s="35"/>
@@ -3162,99 +2898,99 @@
       <c r="AZ21" s="9"/>
     </row>
     <row r="22" spans="1:52" ht="15.6">
-      <c r="A22" s="12" t="s">
-        <v>95</v>
+      <c r="A22" s="22">
+        <v>0.05</v>
       </c>
       <c r="B22" s="28">
-        <v>0.18006944444444445</v>
+        <v>0.20196759259259259</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D22" s="29">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E22" s="12">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="F22" s="12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G22" s="32">
-        <v>9.77</v>
+        <v>2.61</v>
       </c>
       <c r="H22" s="34">
-        <v>6.14</v>
+        <v>7.5</v>
       </c>
       <c r="I22" s="34">
-        <v>26.93</v>
-      </c>
-      <c r="J22" s="9">
-        <v>224</v>
-      </c>
-      <c r="K22" s="13">
-        <v>7.1</v>
-      </c>
-      <c r="L22" s="13">
-        <v>24.07</v>
+        <v>33.86</v>
+      </c>
+      <c r="J22" s="30">
+        <v>250</v>
+      </c>
+      <c r="K22" s="30">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="L22" s="37">
+        <v>43.72</v>
       </c>
       <c r="M22" s="38">
-        <v>6.0778223871928896E-2</v>
-      </c>
-      <c r="N22" s="31">
-        <v>1.71</v>
-      </c>
-      <c r="O22" s="21">
-        <v>6.45</v>
-      </c>
-      <c r="P22" s="21">
-        <v>34.380000000000003</v>
-      </c>
-      <c r="Q22" s="21">
-        <v>90.24</v>
-      </c>
-      <c r="R22" s="31">
-        <v>91.8</v>
-      </c>
-      <c r="S22" s="31">
-        <v>51</v>
-      </c>
-      <c r="T22" s="31">
-        <v>187</v>
-      </c>
-      <c r="U22" s="31">
-        <v>1.56</v>
-      </c>
-      <c r="V22" s="31">
-        <v>13.87</v>
-      </c>
-      <c r="W22" s="31">
-        <v>289</v>
-      </c>
-      <c r="X22" s="31">
-        <v>117.69</v>
-      </c>
-      <c r="Y22" s="31">
-        <v>482.24</v>
-      </c>
-      <c r="Z22" s="31">
-        <v>3</v>
-      </c>
-      <c r="AA22" s="9">
-        <v>7.19</v>
-      </c>
-      <c r="AB22" s="9">
-        <v>2.16</v>
-      </c>
-      <c r="AC22" s="9">
-        <v>72.77</v>
-      </c>
-      <c r="AD22" s="9">
-        <v>62.15</v>
-      </c>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="35">
-        <v>61.72</v>
+        <v>9.0377260981912136E-2</v>
+      </c>
+      <c r="N22" s="39">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="O22" s="40">
+        <v>3.05</v>
+      </c>
+      <c r="P22" s="40">
+        <v>34.32</v>
+      </c>
+      <c r="Q22" s="40">
+        <v>83.94</v>
+      </c>
+      <c r="R22" s="30">
+        <v>75.73</v>
+      </c>
+      <c r="S22" s="30">
+        <v>243</v>
+      </c>
+      <c r="T22" s="30">
+        <v>165</v>
+      </c>
+      <c r="U22" s="30">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="V22" s="30">
+        <v>11.24</v>
+      </c>
+      <c r="W22" s="30">
+        <v>243</v>
+      </c>
+      <c r="X22" s="30">
+        <v>107.7</v>
+      </c>
+      <c r="Y22" s="30">
+        <v>583.91</v>
+      </c>
+      <c r="Z22" s="30">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="30">
+        <v>6.47</v>
+      </c>
+      <c r="AB22" s="30">
+        <v>2.57</v>
+      </c>
+      <c r="AC22" s="30">
+        <v>55.29</v>
+      </c>
+      <c r="AD22" s="30">
+        <v>63.73</v>
+      </c>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="41">
+        <v>56.17</v>
       </c>
       <c r="AG22" s="35"/>
       <c r="AH22" s="35"/>
@@ -3277,103 +3013,103 @@
       <c r="AY22" s="9"/>
       <c r="AZ22" s="9"/>
     </row>
-    <row r="23" spans="1:52" ht="15.6">
-      <c r="A23" s="12" t="s">
-        <v>96</v>
+    <row r="23" spans="1:52">
+      <c r="A23" s="23">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="B23" s="28">
-        <v>0.41905092592592591</v>
+        <v>0.80834490740740739</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D23" s="29">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E23" s="12">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="F23" s="12">
-        <v>37</v>
-      </c>
-      <c r="G23" s="32">
-        <v>8.06</v>
-      </c>
-      <c r="H23" s="34">
-        <v>7.72</v>
-      </c>
-      <c r="I23" s="34">
-        <v>37.64</v>
-      </c>
-      <c r="J23" s="9">
-        <v>201</v>
-      </c>
-      <c r="K23" s="13">
-        <v>7.23</v>
-      </c>
-      <c r="L23" s="13">
-        <v>30.73</v>
+        <v>42</v>
+      </c>
+      <c r="G23" s="13">
+        <v>8.6</v>
+      </c>
+      <c r="H23" s="13">
+        <v>7.17</v>
+      </c>
+      <c r="I23" s="13">
+        <v>20.54</v>
+      </c>
+      <c r="J23" s="30">
+        <v>198</v>
+      </c>
+      <c r="K23" s="30">
+        <v>1.45</v>
+      </c>
+      <c r="L23" s="37">
+        <v>35.450000000000003</v>
       </c>
       <c r="M23" s="38">
-        <v>6.1714262762581837E-2</v>
-      </c>
-      <c r="N23" s="31">
-        <v>5.96</v>
-      </c>
-      <c r="O23" s="21">
-        <v>7.13</v>
-      </c>
-      <c r="P23" s="21">
-        <v>33.35</v>
-      </c>
-      <c r="Q23" s="21">
-        <v>84.56</v>
-      </c>
-      <c r="R23" s="31">
-        <v>69.489999999999995</v>
-      </c>
-      <c r="S23" s="31">
-        <v>63</v>
-      </c>
-      <c r="T23" s="31">
-        <v>113</v>
-      </c>
-      <c r="U23" s="31">
-        <v>1.04</v>
-      </c>
-      <c r="V23" s="31">
-        <v>21.83</v>
-      </c>
-      <c r="W23" s="31">
-        <v>196</v>
-      </c>
-      <c r="X23" s="31">
-        <v>78.83</v>
-      </c>
-      <c r="Y23" s="31">
-        <v>123.63</v>
-      </c>
-      <c r="Z23" s="31">
-        <v>2</v>
-      </c>
-      <c r="AA23" s="9">
-        <v>7.37</v>
-      </c>
-      <c r="AB23" s="9">
-        <v>1.74</v>
-      </c>
-      <c r="AC23" s="9">
-        <v>64.63</v>
-      </c>
-      <c r="AD23" s="9">
-        <v>56.04</v>
-      </c>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="35">
-        <v>48.98</v>
-      </c>
-      <c r="AG23" s="35"/>
-      <c r="AH23" s="35"/>
+        <v>7.6654449525910079E-2</v>
+      </c>
+      <c r="N23" s="39">
+        <v>1.88</v>
+      </c>
+      <c r="O23" s="40">
+        <v>3.91</v>
+      </c>
+      <c r="P23" s="40">
+        <v>36.229999999999997</v>
+      </c>
+      <c r="Q23" s="40">
+        <v>80.63</v>
+      </c>
+      <c r="R23" s="30">
+        <v>58.86</v>
+      </c>
+      <c r="S23" s="30">
+        <v>233</v>
+      </c>
+      <c r="T23" s="30">
+        <v>120</v>
+      </c>
+      <c r="U23" s="30">
+        <v>1.88</v>
+      </c>
+      <c r="V23" s="30">
+        <v>22.6</v>
+      </c>
+      <c r="W23" s="30">
+        <v>179</v>
+      </c>
+      <c r="X23" s="30">
+        <v>58.44</v>
+      </c>
+      <c r="Y23" s="30">
+        <v>489.92</v>
+      </c>
+      <c r="Z23" s="30">
+        <v>4</v>
+      </c>
+      <c r="AA23" s="30">
+        <v>3.32</v>
+      </c>
+      <c r="AB23" s="30">
+        <v>1.61</v>
+      </c>
+      <c r="AC23" s="30">
+        <v>74.849999999999994</v>
+      </c>
+      <c r="AD23" s="30">
+        <v>54.74</v>
+      </c>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="41">
+        <v>31.16</v>
+      </c>
+      <c r="AG23" s="9"/>
+      <c r="AH23" s="9"/>
       <c r="AI23" s="9"/>
       <c r="AJ23" s="9"/>
       <c r="AK23" s="9"/>
@@ -3393,103 +3129,103 @@
       <c r="AY23" s="9"/>
       <c r="AZ23" s="9"/>
     </row>
-    <row r="24" spans="1:52" ht="15.6">
+    <row r="24" spans="1:52">
       <c r="A24" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B24" s="28">
-        <v>0.8825925925925926</v>
+        <v>0.45627314814814812</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D24" s="29">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E24" s="12">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="F24" s="12">
-        <v>40</v>
-      </c>
-      <c r="G24" s="32">
-        <v>3.5</v>
-      </c>
-      <c r="H24" s="34">
-        <v>6.08</v>
-      </c>
-      <c r="I24" s="34">
-        <v>26.65</v>
-      </c>
-      <c r="J24" s="9">
-        <v>155</v>
+        <v>36</v>
+      </c>
+      <c r="G24" s="13">
+        <v>4.7</v>
+      </c>
+      <c r="H24" s="13">
+        <v>4.24</v>
+      </c>
+      <c r="I24" s="13">
+        <v>36.08</v>
+      </c>
+      <c r="J24" s="13">
+        <v>140</v>
       </c>
       <c r="K24" s="13">
-        <v>1.57</v>
+        <v>2.54</v>
       </c>
       <c r="L24" s="13">
-        <v>21.24</v>
+        <v>88.54</v>
       </c>
       <c r="M24" s="38">
-        <v>5.416156670746633E-2</v>
-      </c>
-      <c r="N24" s="21">
-        <v>5.68</v>
+        <v>0.32375310808834284</v>
+      </c>
+      <c r="N24" s="31">
+        <v>0.43</v>
       </c>
       <c r="O24" s="21">
-        <v>2.09</v>
+        <v>6.43</v>
       </c>
       <c r="P24" s="21">
-        <v>33.31</v>
+        <v>37.24</v>
       </c>
       <c r="Q24" s="21">
-        <v>89.04</v>
+        <v>85.76</v>
       </c>
       <c r="R24" s="31">
-        <v>120.81</v>
+        <v>139.36000000000001</v>
       </c>
       <c r="S24" s="31">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="T24" s="31">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="U24" s="31">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="V24" s="31">
-        <v>16.62</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="W24" s="31">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="X24" s="31">
-        <v>149.44999999999999</v>
+        <v>71.52</v>
       </c>
       <c r="Y24" s="31">
-        <v>250.87</v>
+        <v>211.14</v>
       </c>
       <c r="Z24" s="31">
         <v>3</v>
       </c>
       <c r="AA24" s="9">
-        <v>6.16</v>
+        <v>2.46</v>
       </c>
       <c r="AB24" s="9">
-        <v>2.11</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="AC24" s="9">
-        <v>62.51</v>
+        <v>55.22</v>
       </c>
       <c r="AD24" s="9">
-        <v>55.86</v>
+        <v>57.54</v>
       </c>
       <c r="AE24" s="9"/>
-      <c r="AF24" s="9">
-        <v>63.3</v>
-      </c>
-      <c r="AG24" s="9"/>
-      <c r="AH24" s="9"/>
+      <c r="AF24" s="35">
+        <v>24.22</v>
+      </c>
+      <c r="AG24" s="35"/>
+      <c r="AH24" s="35"/>
       <c r="AI24" s="9"/>
       <c r="AJ24" s="9"/>
       <c r="AK24" s="9"/>
@@ -3509,103 +3245,103 @@
       <c r="AY24" s="9"/>
       <c r="AZ24" s="9"/>
     </row>
-    <row r="25" spans="1:52">
+    <row r="25" spans="1:52" ht="15.6">
       <c r="A25" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B25" s="28">
-        <v>0.583587962962963</v>
+        <v>0.18006944444444445</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D25" s="29">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E25" s="12">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="F25" s="12">
-        <v>39</v>
-      </c>
-      <c r="G25" s="13">
-        <v>6.98</v>
-      </c>
-      <c r="H25" s="13">
-        <v>2.08</v>
-      </c>
-      <c r="I25" s="13">
-        <v>36.99</v>
-      </c>
-      <c r="J25" s="13">
-        <v>191</v>
+        <v>42</v>
+      </c>
+      <c r="G25" s="32">
+        <v>9.77</v>
+      </c>
+      <c r="H25" s="34">
+        <v>6.14</v>
+      </c>
+      <c r="I25" s="34">
+        <v>26.93</v>
+      </c>
+      <c r="J25" s="9">
+        <v>224</v>
       </c>
       <c r="K25" s="13">
-        <v>1.1399999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="L25" s="13">
-        <v>75.53</v>
+        <v>24.07</v>
       </c>
       <c r="M25" s="38">
-        <v>0.56298449612403101</v>
-      </c>
-      <c r="N25" s="21">
-        <v>5.81</v>
+        <v>6.0778223871928896E-2</v>
+      </c>
+      <c r="N25" s="31">
+        <v>1.71</v>
       </c>
       <c r="O25" s="21">
-        <v>6.01</v>
+        <v>6.45</v>
       </c>
       <c r="P25" s="21">
-        <v>34.729999999999997</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="Q25" s="21">
-        <v>80.66</v>
-      </c>
-      <c r="R25" s="13">
-        <v>88.67</v>
-      </c>
-      <c r="S25" s="13">
-        <v>146</v>
-      </c>
-      <c r="T25" s="13">
-        <v>120</v>
-      </c>
-      <c r="U25" s="13">
-        <v>1.55</v>
-      </c>
-      <c r="V25" s="13">
-        <v>24.43</v>
-      </c>
-      <c r="W25" s="13">
-        <v>288</v>
-      </c>
-      <c r="X25" s="13">
-        <v>67.48</v>
-      </c>
-      <c r="Y25" s="13">
-        <v>490.84</v>
-      </c>
-      <c r="Z25" s="13">
+        <v>90.24</v>
+      </c>
+      <c r="R25" s="31">
+        <v>91.8</v>
+      </c>
+      <c r="S25" s="31">
+        <v>51</v>
+      </c>
+      <c r="T25" s="31">
+        <v>187</v>
+      </c>
+      <c r="U25" s="31">
+        <v>1.56</v>
+      </c>
+      <c r="V25" s="31">
+        <v>13.87</v>
+      </c>
+      <c r="W25" s="31">
+        <v>289</v>
+      </c>
+      <c r="X25" s="31">
+        <v>117.69</v>
+      </c>
+      <c r="Y25" s="31">
+        <v>482.24</v>
+      </c>
+      <c r="Z25" s="31">
         <v>3</v>
       </c>
       <c r="AA25" s="9">
-        <v>6.83</v>
+        <v>7.19</v>
       </c>
       <c r="AB25" s="9">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="AC25" s="9">
-        <v>58.65</v>
+        <v>72.77</v>
       </c>
       <c r="AD25" s="9">
-        <v>66.959999999999994</v>
+        <v>62.15</v>
       </c>
       <c r="AE25" s="9"/>
-      <c r="AF25" s="9">
-        <v>26.53</v>
-      </c>
-      <c r="AG25" s="9"/>
-      <c r="AH25" s="9"/>
+      <c r="AF25" s="35">
+        <v>61.72</v>
+      </c>
+      <c r="AG25" s="35"/>
+      <c r="AH25" s="35"/>
       <c r="AI25" s="9"/>
       <c r="AJ25" s="9"/>
       <c r="AK25" s="9"/>
@@ -3625,41 +3361,103 @@
       <c r="AY25" s="9"/>
       <c r="AZ25" s="9"/>
     </row>
-    <row r="26" spans="1:52">
-      <c r="A26" s="7"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="9"/>
+    <row r="26" spans="1:52" ht="15.6">
+      <c r="A26" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="28">
+        <v>0.41905092592592591</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="29">
+        <v>64</v>
+      </c>
+      <c r="E26" s="12">
+        <v>203</v>
+      </c>
+      <c r="F26" s="12">
+        <v>37</v>
+      </c>
+      <c r="G26" s="32">
+        <v>8.06</v>
+      </c>
+      <c r="H26" s="34">
+        <v>7.72</v>
+      </c>
+      <c r="I26" s="34">
+        <v>37.64</v>
+      </c>
+      <c r="J26" s="9">
+        <v>201</v>
+      </c>
+      <c r="K26" s="13">
+        <v>7.23</v>
+      </c>
+      <c r="L26" s="13">
+        <v>30.73</v>
+      </c>
+      <c r="M26" s="38">
+        <v>6.1714262762581837E-2</v>
+      </c>
+      <c r="N26" s="31">
+        <v>5.96</v>
+      </c>
+      <c r="O26" s="21">
+        <v>7.13</v>
+      </c>
+      <c r="P26" s="21">
+        <v>33.35</v>
+      </c>
+      <c r="Q26" s="21">
+        <v>84.56</v>
+      </c>
+      <c r="R26" s="31">
+        <v>69.489999999999995</v>
+      </c>
+      <c r="S26" s="31">
+        <v>63</v>
+      </c>
+      <c r="T26" s="31">
+        <v>113</v>
+      </c>
+      <c r="U26" s="31">
+        <v>1.04</v>
+      </c>
+      <c r="V26" s="31">
+        <v>21.83</v>
+      </c>
+      <c r="W26" s="31">
+        <v>196</v>
+      </c>
+      <c r="X26" s="31">
+        <v>78.83</v>
+      </c>
+      <c r="Y26" s="31">
+        <v>123.63</v>
+      </c>
+      <c r="Z26" s="31">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="9">
+        <v>7.37</v>
+      </c>
+      <c r="AB26" s="9">
+        <v>1.74</v>
+      </c>
+      <c r="AC26" s="9">
+        <v>64.63</v>
+      </c>
+      <c r="AD26" s="9">
+        <v>56.04</v>
+      </c>
       <c r="AE26" s="9"/>
-      <c r="AF26" s="9"/>
-      <c r="AG26" s="9"/>
-      <c r="AH26" s="9"/>
+      <c r="AF26" s="35">
+        <v>48.98</v>
+      </c>
+      <c r="AG26" s="35"/>
+      <c r="AH26" s="35"/>
       <c r="AI26" s="9"/>
       <c r="AJ26" s="9"/>
       <c r="AK26" s="9"/>
@@ -3679,113 +3477,237 @@
       <c r="AY26" s="9"/>
       <c r="AZ26" s="9"/>
     </row>
-    <row r="27" spans="1:52">
-      <c r="A27" s="7"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="4"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="9"/>
+    <row r="27" spans="1:52" ht="15.6">
+      <c r="A27" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="28">
+        <v>0.8825925925925926</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="29">
+        <v>59</v>
+      </c>
+      <c r="E27" s="12">
+        <v>189</v>
+      </c>
+      <c r="F27" s="12">
+        <v>40</v>
+      </c>
+      <c r="G27" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="H27" s="34">
+        <v>6.08</v>
+      </c>
+      <c r="I27" s="34">
+        <v>26.65</v>
+      </c>
+      <c r="J27" s="9">
+        <v>155</v>
+      </c>
+      <c r="K27" s="13">
+        <v>1.57</v>
+      </c>
+      <c r="L27" s="13">
+        <v>21.24</v>
+      </c>
+      <c r="M27" s="38">
+        <v>5.416156670746633E-2</v>
+      </c>
+      <c r="N27" s="21">
+        <v>5.68</v>
+      </c>
+      <c r="O27" s="21">
+        <v>2.09</v>
+      </c>
+      <c r="P27" s="21">
+        <v>33.31</v>
+      </c>
+      <c r="Q27" s="21">
+        <v>89.04</v>
+      </c>
+      <c r="R27" s="31">
+        <v>120.81</v>
+      </c>
+      <c r="S27" s="31">
+        <v>236</v>
+      </c>
+      <c r="T27" s="31">
+        <v>147</v>
+      </c>
+      <c r="U27" s="31">
+        <v>1.56</v>
+      </c>
+      <c r="V27" s="31">
+        <v>16.62</v>
+      </c>
+      <c r="W27" s="31">
+        <v>264</v>
+      </c>
+      <c r="X27" s="31">
+        <v>149.44999999999999</v>
+      </c>
+      <c r="Y27" s="31">
+        <v>250.87</v>
+      </c>
+      <c r="Z27" s="31">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>6.16</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>2.11</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>62.51</v>
+      </c>
+      <c r="AD27" s="9">
+        <v>55.86</v>
+      </c>
       <c r="AE27" s="9"/>
-      <c r="AF27" s="9"/>
+      <c r="AF27" s="9">
+        <v>63.3</v>
+      </c>
       <c r="AG27" s="9"/>
-      <c r="AH27" s="4"/>
-      <c r="AI27" s="4"/>
-      <c r="AJ27" s="4"/>
-      <c r="AK27" s="4"/>
-      <c r="AL27" s="4"/>
-      <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="4"/>
-      <c r="AP27" s="4"/>
-      <c r="AQ27" s="4"/>
-      <c r="AR27" s="4"/>
-      <c r="AS27" s="4"/>
-      <c r="AT27" s="4"/>
-      <c r="AU27" s="4"/>
-      <c r="AV27" s="4"/>
-      <c r="AW27" s="4"/>
-      <c r="AX27" s="4"/>
-      <c r="AY27" s="4"/>
-      <c r="AZ27" s="4"/>
+      <c r="AH27" s="9"/>
+      <c r="AI27" s="9"/>
+      <c r="AJ27" s="9"/>
+      <c r="AK27" s="9"/>
+      <c r="AL27" s="9"/>
+      <c r="AM27" s="9"/>
+      <c r="AN27" s="9"/>
+      <c r="AO27" s="9"/>
+      <c r="AP27" s="9"/>
+      <c r="AQ27" s="9"/>
+      <c r="AR27" s="9"/>
+      <c r="AS27" s="9"/>
+      <c r="AT27" s="9"/>
+      <c r="AU27" s="9"/>
+      <c r="AV27" s="9"/>
+      <c r="AW27" s="9"/>
+      <c r="AX27" s="9"/>
+      <c r="AY27" s="9"/>
+      <c r="AZ27" s="9"/>
     </row>
     <row r="28" spans="1:52">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4"/>
-      <c r="AB28" s="4"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="4"/>
-      <c r="AE28" s="4"/>
-      <c r="AF28" s="4"/>
-      <c r="AG28" s="4"/>
-      <c r="AH28" s="4"/>
-      <c r="AI28" s="4"/>
-      <c r="AJ28" s="4"/>
-      <c r="AK28" s="4"/>
-      <c r="AL28" s="4"/>
-      <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="4"/>
-      <c r="AP28" s="4"/>
-      <c r="AQ28" s="4"/>
-      <c r="AR28" s="4"/>
-      <c r="AS28" s="4"/>
-      <c r="AT28" s="4"/>
-      <c r="AU28" s="4"/>
-      <c r="AV28" s="4"/>
-      <c r="AW28" s="4"/>
-      <c r="AX28" s="4"/>
-      <c r="AY28" s="4"/>
-      <c r="AZ28" s="4"/>
+      <c r="A28" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="28">
+        <v>0.583587962962963</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="29">
+        <v>63</v>
+      </c>
+      <c r="E28" s="12">
+        <v>207</v>
+      </c>
+      <c r="F28" s="12">
+        <v>39</v>
+      </c>
+      <c r="G28" s="13">
+        <v>6.98</v>
+      </c>
+      <c r="H28" s="13">
+        <v>2.08</v>
+      </c>
+      <c r="I28" s="13">
+        <v>36.99</v>
+      </c>
+      <c r="J28" s="13">
+        <v>191</v>
+      </c>
+      <c r="K28" s="13">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="L28" s="13">
+        <v>75.53</v>
+      </c>
+      <c r="M28" s="38">
+        <v>0.56298449612403101</v>
+      </c>
+      <c r="N28" s="21">
+        <v>5.81</v>
+      </c>
+      <c r="O28" s="21">
+        <v>6.01</v>
+      </c>
+      <c r="P28" s="21">
+        <v>34.729999999999997</v>
+      </c>
+      <c r="Q28" s="21">
+        <v>80.66</v>
+      </c>
+      <c r="R28" s="13">
+        <v>88.67</v>
+      </c>
+      <c r="S28" s="13">
+        <v>146</v>
+      </c>
+      <c r="T28" s="13">
+        <v>120</v>
+      </c>
+      <c r="U28" s="13">
+        <v>1.55</v>
+      </c>
+      <c r="V28" s="13">
+        <v>24.43</v>
+      </c>
+      <c r="W28" s="13">
+        <v>288</v>
+      </c>
+      <c r="X28" s="13">
+        <v>67.48</v>
+      </c>
+      <c r="Y28" s="13">
+        <v>490.84</v>
+      </c>
+      <c r="Z28" s="13">
+        <v>3</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>6.83</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>1.89</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>58.65</v>
+      </c>
+      <c r="AD28" s="9">
+        <v>66.959999999999994</v>
+      </c>
+      <c r="AE28" s="9"/>
+      <c r="AF28" s="9">
+        <v>26.53</v>
+      </c>
+      <c r="AG28" s="9"/>
+      <c r="AH28" s="9"/>
+      <c r="AI28" s="9"/>
+      <c r="AJ28" s="9"/>
+      <c r="AK28" s="9"/>
+      <c r="AL28" s="9"/>
+      <c r="AM28" s="9"/>
+      <c r="AN28" s="9"/>
+      <c r="AO28" s="9"/>
+      <c r="AP28" s="9"/>
+      <c r="AQ28" s="9"/>
+      <c r="AR28" s="9"/>
+      <c r="AS28" s="9"/>
+      <c r="AT28" s="9"/>
+      <c r="AU28" s="9"/>
+      <c r="AV28" s="9"/>
+      <c r="AW28" s="9"/>
+      <c r="AX28" s="9"/>
+      <c r="AY28" s="9"/>
+      <c r="AZ28" s="9"/>
     </row>
     <row r="29" spans="1:52">
       <c r="A29" s="4"/>
@@ -4004,23 +3926,22 @@
       <c r="AZ32" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AI11:AX11"/>
-    <mergeCell ref="AY11:AZ11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="R11:Z11"/>
-    <mergeCell ref="AA11:AD11"/>
-    <mergeCell ref="AE11:AH11"/>
+  <mergeCells count="15">
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="G1:M2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="F5:G5"/>
+    <mergeCell ref="AI14:AX14"/>
+    <mergeCell ref="AY14:AZ14"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="R14:Z14"/>
+    <mergeCell ref="AA14:AD14"/>
+    <mergeCell ref="AE14:AH14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4041,23 +3962,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="25.8">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -4099,19 +4020,19 @@
       <c r="AZ1" s="4"/>
     </row>
     <row r="2" spans="1:52" ht="25.8">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -4218,10 +4139,10 @@
       <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="58">
         <v>0</v>
       </c>
-      <c r="G4" s="51"/>
+      <c r="G4" s="59"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="4"/>
@@ -4334,7 +4255,7 @@
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="51">
         <v>45633</v>
       </c>
       <c r="C6" s="49"/>
@@ -4725,70 +4646,70 @@
       <c r="F11" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G11" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
       <c r="L11" s="12" t="s">
         <v>14</v>
       </c>
       <c r="M11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="53" t="s">
+      <c r="N11" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
-      <c r="R11" s="55" t="s">
+      <c r="O11" s="47"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="55"/>
-      <c r="AA11" s="52" t="s">
+      <c r="S11" s="50"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="50"/>
+      <c r="W11" s="50"/>
+      <c r="X11" s="50"/>
+      <c r="Y11" s="50"/>
+      <c r="Z11" s="50"/>
+      <c r="AA11" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52" t="s">
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="53" t="s">
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="AJ11" s="53"/>
-      <c r="AK11" s="53"/>
-      <c r="AL11" s="53"/>
-      <c r="AM11" s="53"/>
-      <c r="AN11" s="53"/>
-      <c r="AO11" s="53"/>
-      <c r="AP11" s="53"/>
-      <c r="AQ11" s="53"/>
-      <c r="AR11" s="53"/>
-      <c r="AS11" s="53"/>
-      <c r="AT11" s="53"/>
-      <c r="AU11" s="53"/>
-      <c r="AV11" s="53"/>
-      <c r="AW11" s="53"/>
-      <c r="AX11" s="53"/>
-      <c r="AY11" s="53" t="s">
+      <c r="AJ11" s="47"/>
+      <c r="AK11" s="47"/>
+      <c r="AL11" s="47"/>
+      <c r="AM11" s="47"/>
+      <c r="AN11" s="47"/>
+      <c r="AO11" s="47"/>
+      <c r="AP11" s="47"/>
+      <c r="AQ11" s="47"/>
+      <c r="AR11" s="47"/>
+      <c r="AS11" s="47"/>
+      <c r="AT11" s="47"/>
+      <c r="AU11" s="47"/>
+      <c r="AV11" s="47"/>
+      <c r="AW11" s="47"/>
+      <c r="AX11" s="47"/>
+      <c r="AY11" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="AZ11" s="53"/>
+      <c r="AZ11" s="47"/>
     </row>
     <row r="12" spans="1:52" ht="15.6">
       <c r="A12" s="12"/>
@@ -6858,6 +6779,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="G1:M2"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="AE11:AH11"/>
     <mergeCell ref="AI11:AX11"/>
     <mergeCell ref="AY11:AZ11"/>
@@ -6867,12 +6794,6 @@
     <mergeCell ref="N11:Q11"/>
     <mergeCell ref="R11:Z11"/>
     <mergeCell ref="AA11:AD11"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="G1:M2"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6885,7 +6806,7 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -6893,23 +6814,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="25.8">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -6951,19 +6872,19 @@
       <c r="AZ1" s="4"/>
     </row>
     <row r="2" spans="1:52" ht="25.8">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -7070,10 +6991,10 @@
       <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="58">
         <v>1</v>
       </c>
-      <c r="G4" s="51"/>
+      <c r="G4" s="59"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="4"/>
@@ -7186,7 +7107,7 @@
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="51">
         <v>45684</v>
       </c>
       <c r="C6" s="49"/>
@@ -7244,10 +7165,12 @@
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48">
+      <c r="B7" s="42">
         <v>55</v>
       </c>
-      <c r="C7" s="49"/>
+      <c r="C7" s="45">
+        <v>0.45</v>
+      </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="1"/>
@@ -7356,9 +7279,13 @@
       <c r="AY8" s="4"/>
       <c r="AZ8" s="4"/>
     </row>
-    <row r="9" spans="1:52">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
+    <row r="9" spans="1:52" ht="16.2" thickBot="1">
+      <c r="A9" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="63">
+        <v>10011</v>
+      </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -7410,763 +7337,647 @@
       <c r="AY9" s="4"/>
       <c r="AZ9" s="4"/>
     </row>
-    <row r="10" spans="1:52">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="S10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="T10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="U10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="V10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="X10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AQ10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AS10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AT10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AU10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AX10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AY10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AZ10" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:52" ht="14.4" customHeight="1">
+    <row r="11" spans="1:52" ht="13.8" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="10"/>
+      <c r="D11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AR11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AT11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AX11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AZ11" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:52" ht="14.4" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F12" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="12" t="s">
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M12" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="53" t="s">
+      <c r="N12" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
-      <c r="R11" s="55" t="s">
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="55"/>
-      <c r="AA11" s="52" t="s">
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52" t="s">
+      <c r="AB12" s="12"/>
+      <c r="AC12" s="12"/>
+      <c r="AD12" s="12"/>
+      <c r="AE12" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="53" t="s">
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="AJ11" s="53"/>
-      <c r="AK11" s="53"/>
-      <c r="AL11" s="53"/>
-      <c r="AM11" s="53"/>
-      <c r="AN11" s="53"/>
-      <c r="AO11" s="53"/>
-      <c r="AP11" s="53"/>
-      <c r="AQ11" s="53"/>
-      <c r="AR11" s="53"/>
-      <c r="AS11" s="53"/>
-      <c r="AT11" s="53"/>
-      <c r="AU11" s="53"/>
-      <c r="AV11" s="53"/>
-      <c r="AW11" s="53"/>
-      <c r="AX11" s="53"/>
-      <c r="AY11" s="53" t="s">
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="43"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="43"/>
+      <c r="AX12" s="43"/>
+      <c r="AY12" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="AZ11" s="53"/>
+      <c r="AZ12" s="43"/>
     </row>
-    <row r="12" spans="1:52" ht="15.6">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12" t="s">
+    <row r="13" spans="1:52" ht="15.6">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E13" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G13" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="N13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="O13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="P13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="Q12" s="13" t="s">
+      <c r="Q13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="R12" s="13" t="s">
+      <c r="R13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="T12" s="13" t="s">
+      <c r="T13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="U12" s="13" t="s">
+      <c r="U13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="V13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="W12" s="13" t="s">
+      <c r="W13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="X12" s="13" t="s">
+      <c r="X13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="Y12" s="13" t="s">
+      <c r="Y13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="Z12" s="13" t="s">
+      <c r="Z13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AA12" s="13" t="s">
+      <c r="AA13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AB12" s="13" t="s">
+      <c r="AB13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AC12" s="13" t="s">
+      <c r="AC13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AD12" s="13" t="s">
+      <c r="AD13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AE12" s="13" t="s">
+      <c r="AE13" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AF12" s="13" t="s">
+      <c r="AF13" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AG12" s="13" t="s">
+      <c r="AG13" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AH12" s="13" t="s">
+      <c r="AH13" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AI12" s="9" t="s">
+      <c r="AI13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AJ12" s="9" t="s">
+      <c r="AJ13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AK12" s="9" t="s">
+      <c r="AK13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AL12" s="9" t="s">
+      <c r="AL13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AM12" s="9" t="s">
+      <c r="AM13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AN12" s="9" t="s">
+      <c r="AN13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AO12" s="9" t="s">
+      <c r="AO13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AP12" s="9" t="s">
+      <c r="AP13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AQ12" s="9" t="s">
+      <c r="AQ13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AR12" s="9" t="s">
+      <c r="AR13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AS12" s="9" t="s">
+      <c r="AS13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AT12" s="9" t="s">
+      <c r="AT13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AU12" s="9" t="s">
+      <c r="AU13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AV12" s="9" t="s">
+      <c r="AV13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AW12" s="9" t="s">
+      <c r="AW13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AX12" s="9" t="s">
+      <c r="AX13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AY12" s="13" t="s">
+      <c r="AY13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AZ12" s="13" t="s">
+      <c r="AZ13" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="15" thickBot="1">
-      <c r="A13" s="15" t="s">
+    <row r="14" spans="1:52" ht="15" thickBot="1">
+      <c r="A14" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B14" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C14" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E14" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H14" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I14" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J14" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L14" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="M14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="N14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="O13" s="16" t="s">
+      <c r="O14" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="P13" s="16" t="s">
+      <c r="P14" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="16" t="s">
+      <c r="Q14" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="R13" s="17" t="s">
+      <c r="R14" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="S13" s="18" t="s">
+      <c r="S14" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="T13" s="18" t="s">
+      <c r="T14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="U13" s="18" t="s">
+      <c r="U14" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="V13" s="18" t="s">
+      <c r="V14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="W13" s="18" t="s">
+      <c r="W14" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="X13" s="18" t="s">
+      <c r="X14" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="Y13" s="18" t="s">
+      <c r="Y14" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="Z13" s="18" t="s">
+      <c r="Z14" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="AA13" s="18" t="s">
+      <c r="AA14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="AB13" s="18" t="s">
+      <c r="AB14" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="AC13" s="18" t="s">
+      <c r="AC14" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="AD13" s="18" t="s">
+      <c r="AD14" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="AE13" s="18" t="s">
+      <c r="AE14" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="AF13" s="17" t="s">
+      <c r="AF14" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="AG13" s="17" t="s">
+      <c r="AG14" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="AH13" s="17" t="s">
+      <c r="AH14" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="AI13" s="19" t="s">
+      <c r="AI14" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="AJ13" s="19" t="s">
+      <c r="AJ14" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="AK13" s="19" t="s">
+      <c r="AK14" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="AL13" s="19" t="s">
+      <c r="AL14" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="AM13" s="19" t="s">
+      <c r="AM14" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="AN13" s="19" t="s">
+      <c r="AN14" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="AO13" s="19" t="s">
+      <c r="AO14" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="AP13" s="19" t="s">
+      <c r="AP14" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="AQ13" s="19" t="s">
+      <c r="AQ14" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="AR13" s="19" t="s">
+      <c r="AR14" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="AS13" s="19" t="s">
+      <c r="AS14" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="AT13" s="19" t="s">
+      <c r="AT14" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="AU13" s="19" t="s">
+      <c r="AU14" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="AV13" s="19" t="s">
+      <c r="AV14" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="AW13" s="19" t="s">
+      <c r="AW14" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="AX13" s="19" t="s">
+      <c r="AX14" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="AY13" s="17" t="s">
+      <c r="AY14" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="AZ13" s="17" t="s">
+      <c r="AZ14" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:52">
-      <c r="A14" s="20" t="s">
+    <row r="15" spans="1:52">
+      <c r="A15" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B15" s="28">
         <v>0.31381944444444443</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="29">
-        <v>52</v>
-      </c>
-      <c r="E14" s="29">
-        <v>225</v>
-      </c>
-      <c r="F14" s="29">
-        <v>40</v>
-      </c>
-      <c r="G14" s="30">
-        <v>6.18</v>
-      </c>
-      <c r="H14" s="36">
-        <v>2.7</v>
-      </c>
-      <c r="I14" s="30">
-        <v>24.17</v>
-      </c>
-      <c r="J14" s="30">
-        <v>329</v>
-      </c>
-      <c r="K14" s="30">
-        <v>8.2100000000000009</v>
-      </c>
-      <c r="L14" s="30">
-        <v>34.65</v>
-      </c>
-      <c r="M14" s="38">
-        <v>0.19896640826873382</v>
-      </c>
-      <c r="N14" s="36">
-        <v>0.93</v>
-      </c>
-      <c r="O14" s="40">
-        <v>12.1</v>
-      </c>
-      <c r="P14" s="40">
-        <v>35.82</v>
-      </c>
-      <c r="Q14" s="40">
-        <v>90.14</v>
-      </c>
-      <c r="R14" s="39">
-        <v>116.92</v>
-      </c>
-      <c r="S14" s="39">
-        <v>140</v>
-      </c>
-      <c r="T14" s="39">
-        <v>238</v>
-      </c>
-      <c r="U14" s="39">
-        <v>1.64</v>
-      </c>
-      <c r="V14" s="39">
-        <v>23.5</v>
-      </c>
-      <c r="W14" s="39">
-        <v>182</v>
-      </c>
-      <c r="X14" s="39">
-        <v>113.38</v>
-      </c>
-      <c r="Y14" s="39">
-        <v>352.87</v>
-      </c>
-      <c r="Z14" s="39">
-        <v>2</v>
-      </c>
-      <c r="AA14" s="30">
-        <v>5.15</v>
-      </c>
-      <c r="AB14" s="30">
-        <v>1.62</v>
-      </c>
-      <c r="AC14" s="30">
-        <v>56.57</v>
-      </c>
-      <c r="AD14" s="30">
-        <v>63.1</v>
-      </c>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="30">
-        <v>71.83</v>
-      </c>
-      <c r="AG14" s="33"/>
-      <c r="AH14" s="33"/>
-      <c r="AI14" s="9"/>
-      <c r="AJ14" s="9"/>
-      <c r="AK14" s="9"/>
-      <c r="AL14" s="9"/>
-      <c r="AM14" s="9"/>
-      <c r="AN14" s="9"/>
-      <c r="AO14" s="9"/>
-      <c r="AP14" s="9"/>
-      <c r="AQ14" s="9"/>
-      <c r="AR14" s="9"/>
-      <c r="AS14" s="9"/>
-      <c r="AT14" s="9"/>
-      <c r="AU14" s="9"/>
-      <c r="AV14" s="9"/>
-      <c r="AW14" s="9"/>
-      <c r="AX14" s="9"/>
-      <c r="AY14" s="9"/>
-      <c r="AZ14" s="9"/>
-    </row>
-    <row r="15" spans="1:52" ht="15.6">
-      <c r="A15" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="28">
-        <v>0.6310069444444445</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D15" s="29">
-        <v>74</v>
-      </c>
-      <c r="E15" s="12">
-        <v>231</v>
-      </c>
-      <c r="F15" s="12">
-        <v>37</v>
-      </c>
-      <c r="G15" s="32">
-        <v>8.0399999999999991</v>
-      </c>
-      <c r="H15" s="34">
-        <v>3.94</v>
-      </c>
-      <c r="I15" s="34">
-        <v>36.65</v>
+        <v>52</v>
+      </c>
+      <c r="E15" s="29">
+        <v>225</v>
+      </c>
+      <c r="F15" s="29">
+        <v>40</v>
+      </c>
+      <c r="G15" s="30">
+        <v>6.18</v>
+      </c>
+      <c r="H15" s="36">
+        <v>2.7</v>
+      </c>
+      <c r="I15" s="30">
+        <v>24.17</v>
       </c>
       <c r="J15" s="30">
-        <v>243</v>
+        <v>329</v>
       </c>
       <c r="K15" s="30">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="L15" s="37">
-        <v>83.33</v>
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="L15" s="30">
+        <v>34.65</v>
       </c>
       <c r="M15" s="38">
-        <v>0.32790304175028528</v>
-      </c>
-      <c r="N15" s="39">
-        <v>3.07</v>
+        <v>0.19896640826873382</v>
+      </c>
+      <c r="N15" s="36">
+        <v>0.93</v>
       </c>
       <c r="O15" s="40">
-        <v>11.34</v>
+        <v>12.1</v>
       </c>
       <c r="P15" s="40">
-        <v>35.96</v>
+        <v>35.82</v>
       </c>
       <c r="Q15" s="40">
-        <v>86.62</v>
-      </c>
-      <c r="R15" s="30">
-        <v>122.48</v>
-      </c>
-      <c r="S15" s="30">
-        <v>70</v>
-      </c>
-      <c r="T15" s="30">
-        <v>231</v>
-      </c>
-      <c r="U15" s="30">
-        <v>1.79</v>
-      </c>
-      <c r="V15" s="30">
-        <v>17.73</v>
-      </c>
-      <c r="W15" s="30">
-        <v>285</v>
-      </c>
-      <c r="X15" s="30">
-        <v>98.95</v>
-      </c>
-      <c r="Y15" s="30">
-        <v>568.04999999999995</v>
-      </c>
-      <c r="Z15" s="30">
-        <v>3</v>
+        <v>90.14</v>
+      </c>
+      <c r="R15" s="39">
+        <v>116.92</v>
+      </c>
+      <c r="S15" s="39">
+        <v>140</v>
+      </c>
+      <c r="T15" s="39">
+        <v>238</v>
+      </c>
+      <c r="U15" s="39">
+        <v>1.64</v>
+      </c>
+      <c r="V15" s="39">
+        <v>23.5</v>
+      </c>
+      <c r="W15" s="39">
+        <v>182</v>
+      </c>
+      <c r="X15" s="39">
+        <v>113.38</v>
+      </c>
+      <c r="Y15" s="39">
+        <v>352.87</v>
+      </c>
+      <c r="Z15" s="39">
+        <v>2</v>
       </c>
       <c r="AA15" s="30">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AB15" s="30">
-        <v>2.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" s="30">
-        <v>58.95</v>
+        <v>56.57</v>
       </c>
       <c r="AD15" s="30">
-        <v>65.89</v>
+        <v>63.1</v>
       </c>
       <c r="AE15" s="30"/>
-      <c r="AF15" s="41">
-        <v>70.239999999999995</v>
-      </c>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
+      <c r="AF15" s="30">
+        <v>71.83</v>
+      </c>
+      <c r="AG15" s="33"/>
+      <c r="AH15" s="33"/>
       <c r="AI15" s="9"/>
       <c r="AJ15" s="9"/>
       <c r="AK15" s="9"/>
@@ -8188,98 +7999,98 @@
     </row>
     <row r="16" spans="1:52" ht="15.6">
       <c r="A16" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16" s="28">
-        <v>0.2668402777777778</v>
+        <v>0.6310069444444445</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D16" s="29">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E16" s="12">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F16" s="12">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G16" s="32">
-        <v>5.27</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="H16" s="34">
-        <v>2.19</v>
+        <v>3.94</v>
       </c>
       <c r="I16" s="34">
-        <v>20</v>
+        <v>36.65</v>
       </c>
       <c r="J16" s="30">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="K16" s="30">
-        <v>9.83</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="L16" s="37">
-        <v>2.42</v>
+        <v>83.33</v>
       </c>
       <c r="M16" s="38">
-        <v>1.7132136915507416E-2</v>
+        <v>0.32790304175028528</v>
       </c>
       <c r="N16" s="39">
-        <v>2.4500000000000002</v>
+        <v>3.07</v>
       </c>
       <c r="O16" s="40">
-        <v>3.49</v>
+        <v>11.34</v>
       </c>
       <c r="P16" s="40">
-        <v>31.65</v>
+        <v>35.96</v>
       </c>
       <c r="Q16" s="40">
-        <v>86.77</v>
+        <v>86.62</v>
       </c>
       <c r="R16" s="30">
-        <v>68.430000000000007</v>
+        <v>122.48</v>
       </c>
       <c r="S16" s="30">
-        <v>224</v>
+        <v>70</v>
       </c>
       <c r="T16" s="30">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="U16" s="30">
-        <v>1.1299999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="V16" s="30">
-        <v>19.64</v>
+        <v>17.73</v>
       </c>
       <c r="W16" s="30">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="X16" s="30">
-        <v>136.28</v>
+        <v>98.95</v>
       </c>
       <c r="Y16" s="30">
-        <v>363.28</v>
+        <v>568.04999999999995</v>
       </c>
       <c r="Z16" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA16" s="30">
-        <v>6.82</v>
+        <v>5</v>
       </c>
       <c r="AB16" s="30">
-        <v>1.98</v>
+        <v>2.77</v>
       </c>
       <c r="AC16" s="30">
-        <v>63.1</v>
+        <v>58.95</v>
       </c>
       <c r="AD16" s="30">
-        <v>63.44</v>
+        <v>65.89</v>
       </c>
       <c r="AE16" s="30"/>
       <c r="AF16" s="41">
-        <v>45.55</v>
+        <v>70.239999999999995</v>
       </c>
       <c r="AG16" s="35"/>
       <c r="AH16" s="35"/>
@@ -8303,99 +8114,99 @@
       <c r="AZ16" s="9"/>
     </row>
     <row r="17" spans="1:52" ht="15.6">
-      <c r="A17" s="22">
-        <v>0.1</v>
+      <c r="A17" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="B17" s="28">
-        <v>0.48422453703703705</v>
+        <v>0.2668402777777778</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D17" s="29">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E17" s="12">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F17" s="12">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G17" s="32">
-        <v>3.19</v>
+        <v>5.27</v>
       </c>
       <c r="H17" s="34">
-        <v>3.42</v>
+        <v>2.19</v>
       </c>
       <c r="I17" s="34">
-        <v>21.11</v>
+        <v>20</v>
       </c>
       <c r="J17" s="30">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="K17" s="30">
-        <v>4.87</v>
+        <v>9.83</v>
       </c>
       <c r="L17" s="37">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="M17" s="38">
-        <v>9.2479260165918668E-3</v>
+        <v>1.7132136915507416E-2</v>
       </c>
       <c r="N17" s="39">
-        <v>4.05</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="O17" s="40">
-        <v>10.61</v>
+        <v>3.49</v>
       </c>
       <c r="P17" s="40">
-        <v>32.770000000000003</v>
+        <v>31.65</v>
       </c>
       <c r="Q17" s="40">
-        <v>83.57</v>
+        <v>86.77</v>
       </c>
       <c r="R17" s="30">
-        <v>132.4</v>
+        <v>68.430000000000007</v>
       </c>
       <c r="S17" s="30">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="T17" s="30">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="U17" s="30">
-        <v>1.07</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="V17" s="30">
-        <v>14.9</v>
+        <v>19.64</v>
       </c>
       <c r="W17" s="30">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="X17" s="30">
-        <v>88.56</v>
+        <v>136.28</v>
       </c>
       <c r="Y17" s="30">
-        <v>358.48</v>
+        <v>363.28</v>
       </c>
       <c r="Z17" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA17" s="30">
-        <v>2.06</v>
+        <v>6.82</v>
       </c>
       <c r="AB17" s="30">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AC17" s="30">
-        <v>70.31</v>
+        <v>63.1</v>
       </c>
       <c r="AD17" s="30">
-        <v>53.67</v>
+        <v>63.44</v>
       </c>
       <c r="AE17" s="30"/>
       <c r="AF17" s="41">
-        <v>19.920000000000002</v>
+        <v>45.55</v>
       </c>
       <c r="AG17" s="35"/>
       <c r="AH17" s="35"/>
@@ -8419,11 +8230,11 @@
       <c r="AZ17" s="9"/>
     </row>
     <row r="18" spans="1:52" ht="15.6">
-      <c r="A18" s="23">
-        <v>7.4999999999999997E-2</v>
+      <c r="A18" s="22">
+        <v>0.1</v>
       </c>
       <c r="B18" s="28">
-        <v>0.41616898148148146</v>
+        <v>0.48422453703703705</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>91</v>
@@ -8432,86 +8243,86 @@
         <v>75</v>
       </c>
       <c r="E18" s="12">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="F18" s="12">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G18" s="32">
-        <v>8.27</v>
+        <v>3.19</v>
       </c>
       <c r="H18" s="34">
-        <v>8.0500000000000007</v>
+        <v>3.42</v>
       </c>
       <c r="I18" s="34">
-        <v>17.670000000000002</v>
+        <v>21.11</v>
       </c>
       <c r="J18" s="30">
-        <v>206</v>
+        <v>328</v>
       </c>
       <c r="K18" s="30">
-        <v>4.1500000000000004</v>
+        <v>4.87</v>
       </c>
       <c r="L18" s="37">
-        <v>65.97</v>
+        <v>2.04</v>
       </c>
       <c r="M18" s="38">
-        <v>0.1270547450527228</v>
+        <v>9.2479260165918668E-3</v>
       </c>
       <c r="N18" s="39">
-        <v>6.67</v>
+        <v>4.05</v>
       </c>
       <c r="O18" s="40">
-        <v>4.5999999999999996</v>
+        <v>10.61</v>
       </c>
       <c r="P18" s="40">
-        <v>34.72</v>
+        <v>32.770000000000003</v>
       </c>
       <c r="Q18" s="40">
-        <v>85.96</v>
+        <v>83.57</v>
       </c>
       <c r="R18" s="30">
-        <v>113.87</v>
+        <v>132.4</v>
       </c>
       <c r="S18" s="30">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="T18" s="30">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="U18" s="30">
         <v>1.07</v>
       </c>
       <c r="V18" s="30">
-        <v>25.25</v>
+        <v>14.9</v>
       </c>
       <c r="W18" s="30">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="X18" s="30">
-        <v>118.68</v>
+        <v>88.56</v>
       </c>
       <c r="Y18" s="30">
-        <v>353.1</v>
+        <v>358.48</v>
       </c>
       <c r="Z18" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA18" s="30">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AB18" s="30">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AC18" s="30">
-        <v>68.98</v>
+        <v>70.31</v>
       </c>
       <c r="AD18" s="30">
-        <v>62.4</v>
+        <v>53.67</v>
       </c>
       <c r="AE18" s="30"/>
       <c r="AF18" s="41">
-        <v>19.18</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="AG18" s="35"/>
       <c r="AH18" s="35"/>
@@ -8535,99 +8346,99 @@
       <c r="AZ18" s="9"/>
     </row>
     <row r="19" spans="1:52" ht="15.6">
-      <c r="A19" s="22">
-        <v>0.05</v>
+      <c r="A19" s="23">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="B19" s="28">
-        <v>0.85552083333333329</v>
+        <v>0.41616898148148146</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D19" s="29">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E19" s="12">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F19" s="12">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G19" s="32">
-        <v>4.9800000000000004</v>
+        <v>8.27</v>
       </c>
       <c r="H19" s="34">
-        <v>8.4600000000000009</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="I19" s="34">
-        <v>21.52</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="J19" s="30">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="K19" s="30">
-        <v>8.0500000000000007</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="L19" s="37">
-        <v>43.74</v>
+        <v>65.97</v>
       </c>
       <c r="M19" s="38">
-        <v>8.0158337456704601E-2</v>
+        <v>0.1270547450527228</v>
       </c>
       <c r="N19" s="39">
-        <v>3.18</v>
+        <v>6.67</v>
       </c>
       <c r="O19" s="40">
-        <v>8.8699999999999992</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="P19" s="40">
-        <v>37.65</v>
+        <v>34.72</v>
       </c>
       <c r="Q19" s="40">
-        <v>84.21</v>
+        <v>85.96</v>
       </c>
       <c r="R19" s="30">
-        <v>120.71</v>
+        <v>113.87</v>
       </c>
       <c r="S19" s="30">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="T19" s="30">
-        <v>104</v>
+        <v>218</v>
       </c>
       <c r="U19" s="30">
-        <v>1.1000000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="V19" s="30">
-        <v>10.75</v>
+        <v>25.25</v>
       </c>
       <c r="W19" s="30">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="X19" s="30">
-        <v>139.03</v>
+        <v>118.68</v>
       </c>
       <c r="Y19" s="30">
-        <v>285.32</v>
+        <v>353.1</v>
       </c>
       <c r="Z19" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA19" s="30">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" s="30">
-        <v>2.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC19" s="30">
-        <v>57.26</v>
+        <v>68.98</v>
       </c>
       <c r="AD19" s="30">
-        <v>58.84</v>
+        <v>62.4</v>
       </c>
       <c r="AE19" s="30"/>
       <c r="AF19" s="41">
-        <v>72.55</v>
+        <v>19.18</v>
       </c>
       <c r="AG19" s="35"/>
       <c r="AH19" s="35"/>
@@ -8650,103 +8461,103 @@
       <c r="AY19" s="9"/>
       <c r="AZ19" s="9"/>
     </row>
-    <row r="20" spans="1:52">
-      <c r="A20" s="23">
-        <v>2.5000000000000001E-2</v>
+    <row r="20" spans="1:52" ht="15.6">
+      <c r="A20" s="22">
+        <v>0.05</v>
       </c>
       <c r="B20" s="28">
-        <v>0.18111111111111111</v>
+        <v>0.85552083333333329</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D20" s="29">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E20" s="12">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="F20" s="12">
-        <v>41</v>
-      </c>
-      <c r="G20" s="13">
-        <v>2.58</v>
-      </c>
-      <c r="H20" s="13">
-        <v>8.2899999999999991</v>
-      </c>
-      <c r="I20" s="13">
-        <v>22.12</v>
+        <v>45</v>
+      </c>
+      <c r="G20" s="32">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="H20" s="34">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="I20" s="34">
+        <v>21.52</v>
       </c>
       <c r="J20" s="30">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="K20" s="30">
-        <v>1.39</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="L20" s="37">
-        <v>42.57</v>
+        <v>43.74</v>
       </c>
       <c r="M20" s="38">
-        <v>7.9613992762364305E-2</v>
+        <v>8.0158337456704601E-2</v>
       </c>
       <c r="N20" s="39">
-        <v>0.48</v>
+        <v>3.18</v>
       </c>
       <c r="O20" s="40">
-        <v>12.78</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="P20" s="40">
-        <v>31.45</v>
+        <v>37.65</v>
       </c>
       <c r="Q20" s="40">
-        <v>80.099999999999994</v>
+        <v>84.21</v>
       </c>
       <c r="R20" s="30">
-        <v>152.41</v>
+        <v>120.71</v>
       </c>
       <c r="S20" s="30">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="T20" s="30">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U20" s="30">
-        <v>1.31</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="V20" s="30">
-        <v>27.7</v>
+        <v>10.75</v>
       </c>
       <c r="W20" s="30">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="X20" s="30">
-        <v>106.96</v>
+        <v>139.03</v>
       </c>
       <c r="Y20" s="30">
-        <v>573.54</v>
+        <v>285.32</v>
       </c>
       <c r="Z20" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA20" s="30">
-        <v>5.64</v>
+        <v>2.19</v>
       </c>
       <c r="AB20" s="30">
-        <v>1.33</v>
+        <v>2.63</v>
       </c>
       <c r="AC20" s="30">
-        <v>64.17</v>
+        <v>57.26</v>
       </c>
       <c r="AD20" s="30">
-        <v>59.48</v>
+        <v>58.84</v>
       </c>
       <c r="AE20" s="30"/>
       <c r="AF20" s="41">
-        <v>62.27</v>
-      </c>
-      <c r="AG20" s="9"/>
-      <c r="AH20" s="9"/>
+        <v>72.55</v>
+      </c>
+      <c r="AG20" s="35"/>
+      <c r="AH20" s="35"/>
       <c r="AI20" s="9"/>
       <c r="AJ20" s="9"/>
       <c r="AK20" s="9"/>
@@ -8767,102 +8578,102 @@
       <c r="AZ20" s="9"/>
     </row>
     <row r="21" spans="1:52">
-      <c r="A21" s="12" t="s">
-        <v>94</v>
+      <c r="A21" s="23">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="B21" s="28">
-        <v>0.53585648148148146</v>
+        <v>0.18111111111111111</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>91</v>
       </c>
       <c r="D21" s="29">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E21" s="12">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="F21" s="12">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G21" s="13">
-        <v>3.96</v>
+        <v>2.58</v>
       </c>
       <c r="H21" s="13">
-        <v>4.9400000000000004</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="I21" s="13">
-        <v>31.86</v>
-      </c>
-      <c r="J21" s="13">
-        <v>244</v>
-      </c>
-      <c r="K21" s="13">
-        <v>9.9</v>
-      </c>
-      <c r="L21" s="13">
-        <v>50.46</v>
+        <v>22.12</v>
+      </c>
+      <c r="J21" s="30">
+        <v>192</v>
+      </c>
+      <c r="K21" s="30">
+        <v>1.39</v>
+      </c>
+      <c r="L21" s="37">
+        <v>42.57</v>
       </c>
       <c r="M21" s="38">
-        <v>0.15836550230675076</v>
-      </c>
-      <c r="N21" s="31">
-        <v>3.94</v>
-      </c>
-      <c r="O21" s="21">
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="P21" s="21">
-        <v>37.880000000000003</v>
-      </c>
-      <c r="Q21" s="21">
-        <v>81.89</v>
-      </c>
-      <c r="R21" s="31">
-        <v>97.93</v>
-      </c>
-      <c r="S21" s="31">
-        <v>147</v>
-      </c>
-      <c r="T21" s="31">
-        <v>137</v>
-      </c>
-      <c r="U21" s="31">
-        <v>1.59</v>
-      </c>
-      <c r="V21" s="31">
-        <v>24.2</v>
-      </c>
-      <c r="W21" s="31">
-        <v>152</v>
-      </c>
-      <c r="X21" s="31">
-        <v>140.99</v>
-      </c>
-      <c r="Y21" s="31">
-        <v>308.22000000000003</v>
-      </c>
-      <c r="Z21" s="31">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="9">
-        <v>6.07</v>
-      </c>
-      <c r="AB21" s="9">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="AC21" s="9">
-        <v>61.88</v>
-      </c>
-      <c r="AD21" s="9">
-        <v>67.55</v>
-      </c>
-      <c r="AE21" s="9"/>
-      <c r="AF21" s="35">
-        <v>21.4</v>
-      </c>
-      <c r="AG21" s="35"/>
-      <c r="AH21" s="35"/>
+        <v>7.9613992762364305E-2</v>
+      </c>
+      <c r="N21" s="39">
+        <v>0.48</v>
+      </c>
+      <c r="O21" s="40">
+        <v>12.78</v>
+      </c>
+      <c r="P21" s="40">
+        <v>31.45</v>
+      </c>
+      <c r="Q21" s="40">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="R21" s="30">
+        <v>152.41</v>
+      </c>
+      <c r="S21" s="30">
+        <v>90</v>
+      </c>
+      <c r="T21" s="30">
+        <v>106</v>
+      </c>
+      <c r="U21" s="30">
+        <v>1.31</v>
+      </c>
+      <c r="V21" s="30">
+        <v>27.7</v>
+      </c>
+      <c r="W21" s="30">
+        <v>235</v>
+      </c>
+      <c r="X21" s="30">
+        <v>106.96</v>
+      </c>
+      <c r="Y21" s="30">
+        <v>573.54</v>
+      </c>
+      <c r="Z21" s="30">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="30">
+        <v>5.64</v>
+      </c>
+      <c r="AB21" s="30">
+        <v>1.33</v>
+      </c>
+      <c r="AC21" s="30">
+        <v>64.17</v>
+      </c>
+      <c r="AD21" s="30">
+        <v>59.48</v>
+      </c>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="41">
+        <v>62.27</v>
+      </c>
+      <c r="AG21" s="9"/>
+      <c r="AH21" s="9"/>
       <c r="AI21" s="9"/>
       <c r="AJ21" s="9"/>
       <c r="AK21" s="9"/>
@@ -8882,43 +8693,101 @@
       <c r="AY21" s="9"/>
       <c r="AZ21" s="9"/>
     </row>
-    <row r="22" spans="1:52" ht="15.6">
+    <row r="22" spans="1:52">
       <c r="A22" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="28"/>
+        <v>94</v>
+      </c>
+      <c r="B22" s="28">
+        <v>0.53585648148148146</v>
+      </c>
       <c r="C22" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
+      <c r="D22" s="29">
+        <v>87</v>
+      </c>
+      <c r="E22" s="12">
+        <v>202</v>
+      </c>
+      <c r="F22" s="12">
+        <v>35</v>
+      </c>
+      <c r="G22" s="13">
+        <v>3.96</v>
+      </c>
+      <c r="H22" s="13">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="I22" s="13">
+        <v>31.86</v>
+      </c>
+      <c r="J22" s="13">
+        <v>244</v>
+      </c>
+      <c r="K22" s="13">
+        <v>9.9</v>
+      </c>
+      <c r="L22" s="13">
+        <v>50.46</v>
+      </c>
+      <c r="M22" s="38">
+        <v>0.15836550230675076</v>
+      </c>
+      <c r="N22" s="31">
+        <v>3.94</v>
+      </c>
+      <c r="O22" s="21">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="P22" s="21">
+        <v>37.880000000000003</v>
+      </c>
+      <c r="Q22" s="21">
+        <v>81.89</v>
+      </c>
+      <c r="R22" s="31">
+        <v>97.93</v>
+      </c>
+      <c r="S22" s="31">
+        <v>147</v>
+      </c>
+      <c r="T22" s="31">
+        <v>137</v>
+      </c>
+      <c r="U22" s="31">
+        <v>1.59</v>
+      </c>
+      <c r="V22" s="31">
+        <v>24.2</v>
+      </c>
+      <c r="W22" s="31">
+        <v>152</v>
+      </c>
+      <c r="X22" s="31">
+        <v>140.99</v>
+      </c>
+      <c r="Y22" s="31">
+        <v>308.22000000000003</v>
+      </c>
+      <c r="Z22" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="9">
+        <v>6.07</v>
+      </c>
+      <c r="AB22" s="9">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AC22" s="9">
+        <v>61.88</v>
+      </c>
+      <c r="AD22" s="9">
+        <v>67.55</v>
+      </c>
       <c r="AE22" s="9"/>
-      <c r="AF22" s="35"/>
+      <c r="AF22" s="35">
+        <v>21.4</v>
+      </c>
       <c r="AG22" s="35"/>
       <c r="AH22" s="35"/>
       <c r="AI22" s="9"/>
@@ -8942,7 +8811,7 @@
     </row>
     <row r="23" spans="1:52" ht="15.6">
       <c r="A23" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="12" t="s">
@@ -9000,7 +8869,7 @@
     </row>
     <row r="24" spans="1:52" ht="15.6">
       <c r="A24" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" s="28"/>
       <c r="C24" s="12" t="s">
@@ -9016,7 +8885,7 @@
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
       <c r="M24" s="38"/>
-      <c r="N24" s="21"/>
+      <c r="N24" s="31"/>
       <c r="O24" s="21"/>
       <c r="P24" s="21"/>
       <c r="Q24" s="21"/>
@@ -9034,9 +8903,9 @@
       <c r="AC24" s="9"/>
       <c r="AD24" s="9"/>
       <c r="AE24" s="9"/>
-      <c r="AF24" s="9"/>
-      <c r="AG24" s="9"/>
-      <c r="AH24" s="9"/>
+      <c r="AF24" s="35"/>
+      <c r="AG24" s="35"/>
+      <c r="AH24" s="35"/>
       <c r="AI24" s="9"/>
       <c r="AJ24" s="9"/>
       <c r="AK24" s="9"/>
@@ -9056,9 +8925,9 @@
       <c r="AY24" s="9"/>
       <c r="AZ24" s="9"/>
     </row>
-    <row r="25" spans="1:52">
+    <row r="25" spans="1:52" ht="15.6">
       <c r="A25" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25" s="28"/>
       <c r="C25" s="12" t="s">
@@ -9067,10 +8936,10 @@
       <c r="D25" s="29"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="9"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="38"/>
@@ -9078,15 +8947,15 @@
       <c r="O25" s="21"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="13"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="13"/>
-      <c r="X25" s="13"/>
-      <c r="Y25" s="13"/>
-      <c r="Z25" s="13"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="31"/>
+      <c r="Z25" s="31"/>
       <c r="AA25" s="9"/>
       <c r="AB25" s="9"/>
       <c r="AC25" s="9"/>
@@ -9115,32 +8984,36 @@
       <c r="AZ25" s="9"/>
     </row>
     <row r="26" spans="1:52">
-      <c r="A26" s="7"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
+      <c r="A26" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="29"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="13"/>
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
       <c r="AA26" s="9"/>
       <c r="AB26" s="9"/>
       <c r="AC26" s="9"/>
@@ -9175,7 +9048,7 @@
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
+      <c r="G27" s="31"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
@@ -9191,7 +9064,7 @@
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
       <c r="V27" s="9"/>
-      <c r="W27" s="4"/>
+      <c r="W27" s="9"/>
       <c r="X27" s="9"/>
       <c r="Y27" s="9"/>
       <c r="Z27" s="9"/>
@@ -9202,25 +9075,25 @@
       <c r="AE27" s="9"/>
       <c r="AF27" s="9"/>
       <c r="AG27" s="9"/>
-      <c r="AH27" s="4"/>
-      <c r="AI27" s="4"/>
-      <c r="AJ27" s="4"/>
-      <c r="AK27" s="4"/>
-      <c r="AL27" s="4"/>
-      <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="4"/>
-      <c r="AP27" s="4"/>
-      <c r="AQ27" s="4"/>
-      <c r="AR27" s="4"/>
-      <c r="AS27" s="4"/>
-      <c r="AT27" s="4"/>
-      <c r="AU27" s="4"/>
-      <c r="AV27" s="4"/>
-      <c r="AW27" s="4"/>
-      <c r="AX27" s="4"/>
-      <c r="AY27" s="4"/>
-      <c r="AZ27" s="4"/>
+      <c r="AH27" s="9"/>
+      <c r="AI27" s="9"/>
+      <c r="AJ27" s="9"/>
+      <c r="AK27" s="9"/>
+      <c r="AL27" s="9"/>
+      <c r="AM27" s="9"/>
+      <c r="AN27" s="9"/>
+      <c r="AO27" s="9"/>
+      <c r="AP27" s="9"/>
+      <c r="AQ27" s="9"/>
+      <c r="AR27" s="9"/>
+      <c r="AS27" s="9"/>
+      <c r="AT27" s="9"/>
+      <c r="AU27" s="9"/>
+      <c r="AV27" s="9"/>
+      <c r="AW27" s="9"/>
+      <c r="AX27" s="9"/>
+      <c r="AY27" s="9"/>
+      <c r="AZ27" s="9"/>
     </row>
     <row r="28" spans="1:52">
       <c r="A28" s="4"/>
@@ -9493,22 +9366,14 @@
       <c r="AZ32" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="AE11:AH11"/>
-    <mergeCell ref="AI11:AX11"/>
-    <mergeCell ref="AY11:AZ11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="R11:Z11"/>
-    <mergeCell ref="AA11:AD11"/>
+  <mergeCells count="7">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="G1:M2"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
